--- a/RC_Catalogo_Questionarios.xlsx
+++ b/RC_Catalogo_Questionarios.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="1051">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="1065">
   <si>
     <t xml:space="preserve">RC · Catálogo de Questionários — Ricardina Correia · OPP 8233</t>
   </si>
@@ -3059,6 +3059,48 @@
   </si>
   <si>
     <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/UCLA_PTSD_Adaptado.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anamnese Parental Complementar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recolha estruturada da perspetiva do progenitor ou cuidador que não esteve presente na consulta de anamnese inicial e deseja integrar o processo de avaliação/intervenção. Instrumento qualitativo de anamnese — sem cotação: regista motivação para participar, preocupação principal e áreas assinaladas, a criança no contexto do respondente (rotinas, o que corre bem, o que é mais difícil), evolução percebida, informação adicional e expectativas/disponibilidade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preocupações principais; Áreas assinaladas; Contexto do respondente; Evolução percebida; Expectativas e disponibilidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anamnese_parental_complementar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_anamnese_parental_complementar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/ANAMNESE_PARENTAL_COMPLEMENTAR_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MABC-2 — Lista de Verificação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professor(a), Educador(a), Mãe, Pai, Enc. Educação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5–12 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rastreio heteroavaliado das dificuldades de coordenação motora no quotidiano (Movement ABC-2 Checklist, Henderson, Sugden &amp; Barnett). Preenchido por adulto que observa a criança: Secção A (movimento em ambiente estático/previsível) e Secção B (movimento em ambiente dinâmico/imprevisível), cada uma 0–3/NO; Secção C regista fatores não motores (Sim/Não). Cotação com imputação por «Não Observado» e semáforo normativo por idade (apenas no painel clínico).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secção A — Estático/Previsível; Secção B — Dinâmico/Imprevisível; Total Motor (A+B); Secção C — Fatores não motores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mabc2_checklist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_mabc2_checklist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/MABC2_Checklist_v1.html</t>
   </si>
   <si>
     <t xml:space="preserve">Resumo por Área Clínica (recalcula automaticamente)</t>
@@ -3542,8 +3584,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M150" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A3:M150"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M152" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A3:M152"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nº"/>
     <tableColumn id="2" name="Nome do Instrumento"/>
@@ -3742,7 +3784,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M150"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -9966,7 +10008,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="5" t="n">
         <f aca="false">ROW()-3</f>
         <v>147</v>
@@ -10006,6 +10048,90 @@
       </c>
       <c r="M150" s="7" t="s">
         <v>1011</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A151" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>148</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F151" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I151" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="J151" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="K151" s="6" t="s">
+        <v>1015</v>
+      </c>
+      <c r="L151" s="6" t="s">
+        <v>1016</v>
+      </c>
+      <c r="M151" s="7" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>149</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F152" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H152" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I152" s="6" t="s">
+        <v>1021</v>
+      </c>
+      <c r="J152" s="6" t="s">
+        <v>1022</v>
+      </c>
+      <c r="K152" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L152" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="M152" s="7" t="s">
+        <v>1025</v>
       </c>
     </row>
   </sheetData>
@@ -10189,7 +10315,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1012</v>
+        <v>1026</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10199,10 +10325,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1013</v>
+        <v>1027</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1014</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10215,7 +10341,7 @@
       </c>
       <c r="C3" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B3/$B$28)</f>
-        <v>0.0408163265306122</v>
+        <v>0.0402684563758389</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10224,11 +10350,11 @@
       </c>
       <c r="B4" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A4)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B4/$B$28)</f>
-        <v>0.0136054421768707</v>
+        <v>0.0201342281879195</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10241,7 +10367,7 @@
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B5/$B$28)</f>
-        <v>0.108843537414966</v>
+        <v>0.10738255033557</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10254,7 +10380,7 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B6/$B$28)</f>
-        <v>0.0884353741496599</v>
+        <v>0.087248322147651</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10267,7 +10393,7 @@
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B7/$B$28)</f>
-        <v>0.0408163265306122</v>
+        <v>0.0402684563758389</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10280,7 +10406,7 @@
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B8/$B$28)</f>
-        <v>0.0272108843537415</v>
+        <v>0.0268456375838926</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10293,7 +10419,7 @@
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B9/$B$28)</f>
-        <v>0.0136054421768707</v>
+        <v>0.0134228187919463</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10306,7 +10432,7 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B10/$B$28)</f>
-        <v>0.00680272108843537</v>
+        <v>0.00671140939597315</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10319,7 +10445,7 @@
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B11/$B$28)</f>
-        <v>0.0272108843537415</v>
+        <v>0.0268456375838926</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10332,7 +10458,7 @@
       </c>
       <c r="C12" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B12/$B$28)</f>
-        <v>0.0816326530612245</v>
+        <v>0.0805369127516779</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10345,7 +10471,7 @@
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B13/$B$28)</f>
-        <v>0.0612244897959184</v>
+        <v>0.0604026845637584</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10358,7 +10484,7 @@
       </c>
       <c r="C14" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B14/$B$28)</f>
-        <v>0.108843537414966</v>
+        <v>0.10738255033557</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10371,7 +10497,7 @@
       </c>
       <c r="C15" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B15/$B$28)</f>
-        <v>0.00680272108843537</v>
+        <v>0.00671140939597315</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10384,7 +10510,7 @@
       </c>
       <c r="C16" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B16/$B$28)</f>
-        <v>0.0136054421768707</v>
+        <v>0.0134228187919463</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10397,7 +10523,7 @@
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B17/$B$28)</f>
-        <v>0.0204081632653061</v>
+        <v>0.0201342281879195</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10410,7 +10536,7 @@
       </c>
       <c r="C18" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B18/$B$28)</f>
-        <v>0.00680272108843537</v>
+        <v>0.00671140939597315</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10423,7 +10549,7 @@
       </c>
       <c r="C19" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B19/$B$28)</f>
-        <v>0.00680272108843537</v>
+        <v>0.00671140939597315</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10432,11 +10558,11 @@
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A20)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B20/$B$28)</f>
-        <v>0.0884353741496599</v>
+        <v>0.0939597315436242</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10449,7 +10575,7 @@
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B21/$B$28)</f>
-        <v>0.0476190476190476</v>
+        <v>0.0469798657718121</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10462,7 +10588,7 @@
       </c>
       <c r="C22" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B22/$B$28)</f>
-        <v>0.00680272108843537</v>
+        <v>0.00671140939597315</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10475,7 +10601,7 @@
       </c>
       <c r="C23" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B23/$B$28)</f>
-        <v>0.0476190476190476</v>
+        <v>0.0469798657718121</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10488,7 +10614,7 @@
       </c>
       <c r="C24" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B24/$B$28)</f>
-        <v>0.0884353741496599</v>
+        <v>0.087248322147651</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10501,7 +10627,7 @@
       </c>
       <c r="C25" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B25/$B$28)</f>
-        <v>0.0204081632653061</v>
+        <v>0.0201342281879195</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10514,7 +10640,7 @@
       </c>
       <c r="C26" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B26/$B$28)</f>
-        <v>0.0204081632653061</v>
+        <v>0.0201342281879195</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10527,16 +10653,16 @@
       </c>
       <c r="C27" s="10" t="n">
         <f aca="false">IF($B$28=0,0,B27/$B$28)</f>
-        <v>0.00680272108843537</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.00671140939597315</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>1015</v>
+        <v>1029</v>
       </c>
       <c r="B28" s="11" t="n">
         <f aca="false">COUNTA(Catálogo!$B$4:$B$1000)</f>
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C28" s="12" t="n">
         <f aca="false">IF(B28=0,0,B28/B28)</f>
@@ -10546,12 +10672,12 @@
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>1017</v>
+        <v>1031</v>
       </c>
       <c r="B31" s="15" t="str">
         <f aca="false">IF(SUM(B3:B27)=B28,"OK","Existe AREA nova - adicionar linha no resumo")</f>
@@ -10587,64 +10713,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1018</v>
+        <v>1032</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>1019</v>
+        <v>1033</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1020</v>
+        <v>1034</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1021</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>1022</v>
+        <v>1036</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1023</v>
+        <v>1037</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1024</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>1025</v>
+        <v>1039</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1026</v>
+        <v>1040</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1027</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>1028</v>
+        <v>1042</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1029</v>
+        <v>1043</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1030</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>1031</v>
+        <v>1045</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1032</v>
+        <v>1046</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1033</v>
+        <v>1047</v>
       </c>
     </row>
   </sheetData>
@@ -10675,56 +10801,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1034</v>
+        <v>1048</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>1035</v>
+        <v>1049</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>1036</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>1037</v>
+        <v>1051</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>1038</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>1039</v>
+        <v>1053</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>1040</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>1041</v>
+        <v>1055</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1042</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>1043</v>
+        <v>1057</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>1044</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>1045</v>
+        <v>1059</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>1046</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10733,18 +10859,18 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>1047</v>
+        <v>1061</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>1048</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>1049</v>
+        <v>1063</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>1050</v>
+        <v>1064</v>
       </c>
     </row>
   </sheetData>

--- a/RC_Catalogo_Questionarios.xlsx
+++ b/RC_Catalogo_Questionarios.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="1108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="1134">
   <si>
     <t xml:space="preserve">RC · Catálogo de Questionários — Ricardina Correia · OPP 8233</t>
   </si>
@@ -3230,6 +3230,84 @@
   </si>
   <si>
     <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/TSOC_YGTSS_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-DES — Escala de Experiências Dissociativas em Adolescentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rastreio dimensional de experiências dissociativas por auto-relato do adolescente (30 itens, escala 0–10). Métrica = média global + 5 domínios (Amnésia; Despersonalização/Desrealização; Absorção; Alteração de Identidade; Transversal). Ponto de corte orientador: média ≥ 4,0 = dissociação clinicamente significativa; 3,0–3,9 = moderada. Instrumento de rastreio/orientação, não diagnóstico — integrar sempre com entrevista clínica, observação e história de vida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amnésia; Despersonalização/Desrealização; Absorção; Alteração de Identidade; Transversal; Média Global A-DES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_ades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/A_DES_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACE-Q — Experiências Adversas na Infância · Autorrelato (Adolescente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rastreio de experiências adversas na infância por autorrelato do adolescente (18 itens, escala de frequência 0–2). Adaptação clínica da ACE-Q (Felitti et al., 1998) / ACE-IQ (WHO, 2010) para 6 domínios. Pontuação total 0–36 com bandas orientadoras (0–8 baixa; 9–18 moderada; &gt;18 elevada) e classificação por domínio. Instrumento de rastreio/orientação, não diagnóstico — integrar sempre com entrevista clínica e história de vida. Os domínios e a pontuação não são visíveis ao respondente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relações familiares e ambiente emocional; Instabilidade familiar; Experiências de perda; Experiências de insegurança ou ameaça; Experiências sociais difíceis; Experiência emocional interna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aceq_adol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_aceq_adol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/ACE-Q_Adolescente.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACE-Q — Experiências Adversas na Infância · Cuidador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rastreio de experiências adversas na infância por relato do cuidador (15 itens, escala de frequência 0–2). Adaptação clínica da ACE-Q (Felitti et al., 1998) e da versão pediátrica PEARLS (Brar et al., 2021) para 6 domínios. Pontuação total 0–30 com bandas orientadoras (0–6 baixa exposição; 7–14 moderada; ≥15 significativa) e classificação por domínio. Instrumento de rastreio/orientação, não diagnóstico — integrar sempre com entrevista clínica e história de vida. Os domínios e a pontuação não são visíveis ao respondente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambiente emocional familiar; Instabilidade familiar; Experiências de perda; Segurança e proteção; Experiências sociais difíceis; Eventos stressantes significativos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aceq_cuid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_aceq_cuid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/ACE-Q_Cuidador.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrevista adaptada CAARMS — Experiências Psicóticas Atenuadas, Dissociação e Funcionamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psicóloga (aplicação clínica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adolescentes / jovens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrevista semiestruturada aplicada pela psicóloga (Avaliação Fenomenológica de Experiências Psicóticas Atenuadas, Dissociação e Funcionamento Subjetivo). Adaptação inspirada (Via B) nos domínios do CAARMS (Yung, McGorry et al., 2005), com formulação original em português europeu — NÃO constitui reprodução do CAARMS. Orientadora e descritiva, não diagnóstica: não classifica risco (UHR/APS/BLIPS). 10 domínios com cotação estruturada 0/1/2 (típico–preservado / intermédio / marcado–ausente); campos vazios cotam 0. A aplicação regista as respostas fluidas ditas pelo próprio, a cotação de cada item e observações qualitativas; o painel apresenta o perfil por domínio, o Índice Global de Alteração Dimensional (IGAD = média dos 10 índices; IGAD bruto = soma/54×100) e um painel de sinalização (11 marcadores Alto/Médio). Bandas orientadoras do IGAD: &lt;34 Mínima / 34–66 Moderada / ≥67 Elevada. Instrumento orientativo, a integrar sempre com entrevista clínica, observação e história de vida. Os domínios e a pontuação não são visíveis ao respondente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experiências percetivas atípicas; Pensamento, fluência e organização cognitiva; Ideias de referência, desconfiança e hipervigilância; Self, corpo e experiências dissociativas; Experiência emocional e afetividade; Funcionamento global e esforço subjetivo; Narrativa subjetiva e organização do discurso; Qualidade de contacto e presença relacional; Insight, significado e medos implícitos; Coerência interna e continuidade do self; IGAD (Índice Global de Alteração Dimensional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caarms_adap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_caarms_adap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/Entrevista_CAARMS_adap.html</t>
   </si>
   <si>
     <t xml:space="preserve">Resumo por Área Clínica (recalcula automaticamente)</t>
@@ -3713,8 +3791,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M158" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A3:M158"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M162" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A3:M162"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nº"/>
     <tableColumn id="2" name="Nome do Instrumento"/>
@@ -3913,7 +3991,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M158"/>
+  <dimension ref="A1:M162"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -10510,6 +10588,173 @@
       </c>
       <c r="M158" s="7" t="s">
         <v>1068</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A159" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F159" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H159" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I159" s="6" t="s">
+        <v>1070</v>
+      </c>
+      <c r="J159" s="6" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K159" s="6" t="s">
+        <v>1072</v>
+      </c>
+      <c r="L159" s="6" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M159" s="7" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A160" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>157</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="F160" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H160" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I160" s="6" t="s">
+        <v>1076</v>
+      </c>
+      <c r="J160" s="6" t="s">
+        <v>1077</v>
+      </c>
+      <c r="K160" s="6" t="s">
+        <v>1078</v>
+      </c>
+      <c r="L160" s="6" t="s">
+        <v>1079</v>
+      </c>
+      <c r="M160" s="7" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A161" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>158</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F161" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H161" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I161" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="J161" s="6" t="s">
+        <v>1083</v>
+      </c>
+      <c r="K161" s="6" t="s">
+        <v>1084</v>
+      </c>
+      <c r="L161" s="6" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M161" s="7" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A162" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>159</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F162" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H162" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I162" s="6" t="s">
+        <v>1090</v>
+      </c>
+      <c r="J162" s="6" t="s">
+        <v>1091</v>
+      </c>
+      <c r="K162" s="6" t="s">
+        <v>1092</v>
+      </c>
+      <c r="L162" s="6" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M162" s="7" t="s">
+        <v>1094</v>
       </c>
     </row>
   </sheetData>
@@ -10693,7 +10938,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1069</v>
+        <v>1095</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10703,10 +10948,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1070</v>
+        <v>1096</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1071</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10719,7 +10964,7 @@
       </c>
       <c r="C3" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B3/$B$29)</f>
-        <v>0.0387096774193548</v>
+        <v>0.0377358490566038</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10732,7 +10977,7 @@
       </c>
       <c r="C4" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B4/$B$29)</f>
-        <v>0.0193548387096774</v>
+        <v>0.0188679245283019</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10745,7 +10990,7 @@
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B5/$B$29)</f>
-        <v>0.103225806451613</v>
+        <v>0.10062893081761</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10758,7 +11003,7 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B6/$B$29)</f>
-        <v>0.0903225806451613</v>
+        <v>0.0880503144654088</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10771,7 +11016,7 @@
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B7/$B$29)</f>
-        <v>0.0387096774193548</v>
+        <v>0.0377358490566038</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10784,7 +11029,7 @@
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B8/$B$29)</f>
-        <v>0.0258064516129032</v>
+        <v>0.0251572327044025</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10797,7 +11042,7 @@
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B9/$B$29)</f>
-        <v>0.0129032258064516</v>
+        <v>0.0125786163522013</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10810,7 +11055,7 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B10/$B$29)</f>
-        <v>0.00645161290322581</v>
+        <v>0.00628930817610063</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10823,7 +11068,7 @@
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B11/$B$29)</f>
-        <v>0.0258064516129032</v>
+        <v>0.0251572327044025</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10836,7 +11081,7 @@
       </c>
       <c r="C12" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B12/$B$29)</f>
-        <v>0.0774193548387097</v>
+        <v>0.0754716981132075</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10849,7 +11094,7 @@
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B13/$B$29)</f>
-        <v>0.0580645161290323</v>
+        <v>0.0566037735849057</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10862,7 +11107,7 @@
       </c>
       <c r="C14" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B14/$B$29)</f>
-        <v>0.103225806451613</v>
+        <v>0.10062893081761</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10875,7 +11120,7 @@
       </c>
       <c r="C15" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B15/$B$29)</f>
-        <v>0.00645161290322581</v>
+        <v>0.00628930817610063</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10888,7 +11133,7 @@
       </c>
       <c r="C16" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B16/$B$29)</f>
-        <v>0.0129032258064516</v>
+        <v>0.0125786163522013</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10901,7 +11146,7 @@
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B17/$B$29)</f>
-        <v>0.0193548387096774</v>
+        <v>0.0188679245283019</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10914,7 +11159,7 @@
       </c>
       <c r="C18" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B18/$B$29)</f>
-        <v>0.00645161290322581</v>
+        <v>0.00628930817610063</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10927,7 +11172,7 @@
       </c>
       <c r="C19" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B19/$B$29)</f>
-        <v>0.00645161290322581</v>
+        <v>0.00628930817610063</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10940,7 +11185,7 @@
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B20/$B$29)</f>
-        <v>0.0967741935483871</v>
+        <v>0.0943396226415094</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10953,7 +11198,7 @@
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B21/$B$29)</f>
-        <v>0.0451612903225806</v>
+        <v>0.0440251572327044</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10966,7 +11211,7 @@
       </c>
       <c r="C22" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B22/$B$29)</f>
-        <v>0.00645161290322581</v>
+        <v>0.00628930817610063</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10979,7 +11224,7 @@
       </c>
       <c r="C23" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B23/$B$29)</f>
-        <v>0.0451612903225806</v>
+        <v>0.0440251572327044</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10992,7 +11237,7 @@
       </c>
       <c r="C24" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B24/$B$29)</f>
-        <v>0.0838709677419355</v>
+        <v>0.0817610062893082</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11001,11 +11246,11 @@
       </c>
       <c r="B25" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A25)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B25/$B$29)</f>
-        <v>0.032258064516129</v>
+        <v>0.0377358490566038</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11018,7 +11263,7 @@
       </c>
       <c r="C26" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B26/$B$29)</f>
-        <v>0.0193548387096774</v>
+        <v>0.0188679245283019</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11031,7 +11276,7 @@
       </c>
       <c r="C27" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B27/$B$29)</f>
-        <v>0.0129032258064516</v>
+        <v>0.0125786163522013</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11040,20 +11285,20 @@
       </c>
       <c r="B28" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A28)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C28" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B28/$B$29)</f>
-        <v>0.00645161290322581</v>
+        <v>0.0251572327044025</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B29" s="11" t="n">
         <f aca="false">COUNTA(Catálogo!$B$4:$B$1000)</f>
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">IF(B29=0,0,B29/B29)</f>
@@ -11063,12 +11308,12 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>1073</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>1074</v>
+        <v>1100</v>
       </c>
       <c r="B32" s="15" t="str">
         <f aca="false">IF(SUM(B3:B28)=B29,"OK","Existe AREA nova - adicionar linha no resumo")</f>
@@ -11104,64 +11349,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1075</v>
+        <v>1101</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>1076</v>
+        <v>1102</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1077</v>
+        <v>1103</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1078</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>1079</v>
+        <v>1105</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1080</v>
+        <v>1106</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1081</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>1082</v>
+        <v>1108</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1083</v>
+        <v>1109</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1084</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>1085</v>
+        <v>1111</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1086</v>
+        <v>1112</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1087</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>1088</v>
+        <v>1114</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1089</v>
+        <v>1115</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1090</v>
+        <v>1116</v>
       </c>
     </row>
   </sheetData>
@@ -11192,56 +11437,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1091</v>
+        <v>1117</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>1092</v>
+        <v>1118</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>1093</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>1094</v>
+        <v>1120</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>1095</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>1096</v>
+        <v>1122</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>1097</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1099</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>1100</v>
+        <v>1126</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>1101</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>1102</v>
+        <v>1128</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>1103</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11250,18 +11495,18 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>1104</v>
+        <v>1130</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>1105</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>1106</v>
+        <v>1132</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>1107</v>
+        <v>1133</v>
       </c>
     </row>
   </sheetData>

--- a/RC_Catalogo_Questionarios.xlsx
+++ b/RC_Catalogo_Questionarios.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="1134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="1141">
   <si>
     <t xml:space="preserve">RC · Catálogo de Questionários — Ricardina Correia · OPP 8233</t>
   </si>
@@ -3308,6 +3308,27 @@
   </si>
   <si>
     <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/Entrevista_CAARMS_adap.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prova «O Cuidar e a Integridade do Corpo»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idade escolar (≈ 6–11 anos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prova projetiva integrada de story-stems abertos (instrumento original de Ricardina Correia, 2026), de aplicação exclusiva pela psicóloga, para avaliação idiográfica e qualitativa do cuidar, da integridade corporal, do coping e das figuras cuidadoras em idade escolar (≈6–11 anos). Administração não-diretiva: não nomear «medo/dor/doença/hospital» antes da criança; sondas condicionais só se o tema emergir; registo do verbatim, hesitações, evitamentos e pedidos de tranquilização; desenho opcional. Leitura descritiva (não-normativa, não-cotação): posicionamento 1 (adaptativo) → 5 (vulnerabilidade) nos eixos, mais reparação relacional no desfecho. Instrumento orientativo, a integrar sempre com entrevista clínica, observação e história de vida. Os eixos e o posicionamento não são visíveis ao respondente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integridade corporal; Cuidado e dependência; Coping / resolução (padrão predominante + secundário); Figuras cuidadoras (+ reparação relacional no desfecho)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cuidar_corpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_cuidar_corpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/Prova_Cuidar_Integridade_Corpo_v1.html</t>
   </si>
   <si>
     <t xml:space="preserve">Resumo por Área Clínica (recalcula automaticamente)</t>
@@ -3791,8 +3812,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M162" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A3:M162"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M163" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A3:M163"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nº"/>
     <tableColumn id="2" name="Nome do Instrumento"/>
@@ -3991,7 +4012,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:M163"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -10755,6 +10776,48 @@
       </c>
       <c r="M162" s="7" t="s">
         <v>1094</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A163" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>160</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F163" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I163" s="6" t="s">
+        <v>1097</v>
+      </c>
+      <c r="J163" s="6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="K163" s="6" t="s">
+        <v>1099</v>
+      </c>
+      <c r="L163" s="6" t="s">
+        <v>1100</v>
+      </c>
+      <c r="M163" s="7" t="s">
+        <v>1101</v>
       </c>
     </row>
   </sheetData>
@@ -10938,7 +11001,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10948,10 +11011,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1096</v>
+        <v>1103</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10964,7 +11027,7 @@
       </c>
       <c r="C3" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B3/$B$29)</f>
-        <v>0.0377358490566038</v>
+        <v>0.0375</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10977,7 +11040,7 @@
       </c>
       <c r="C4" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B4/$B$29)</f>
-        <v>0.0188679245283019</v>
+        <v>0.01875</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10990,7 +11053,7 @@
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B5/$B$29)</f>
-        <v>0.10062893081761</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11003,7 +11066,7 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B6/$B$29)</f>
-        <v>0.0880503144654088</v>
+        <v>0.0875</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11016,7 +11079,7 @@
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B7/$B$29)</f>
-        <v>0.0377358490566038</v>
+        <v>0.0375</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11029,7 +11092,7 @@
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B8/$B$29)</f>
-        <v>0.0251572327044025</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11042,7 +11105,7 @@
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B9/$B$29)</f>
-        <v>0.0125786163522013</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11055,7 +11118,7 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B10/$B$29)</f>
-        <v>0.00628930817610063</v>
+        <v>0.00625</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11068,7 +11131,7 @@
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B11/$B$29)</f>
-        <v>0.0251572327044025</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11081,7 +11144,7 @@
       </c>
       <c r="C12" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B12/$B$29)</f>
-        <v>0.0754716981132075</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11094,7 +11157,7 @@
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B13/$B$29)</f>
-        <v>0.0566037735849057</v>
+        <v>0.05625</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11107,7 +11170,7 @@
       </c>
       <c r="C14" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B14/$B$29)</f>
-        <v>0.10062893081761</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11120,7 +11183,7 @@
       </c>
       <c r="C15" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B15/$B$29)</f>
-        <v>0.00628930817610063</v>
+        <v>0.00625</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11133,7 +11196,7 @@
       </c>
       <c r="C16" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B16/$B$29)</f>
-        <v>0.0125786163522013</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11146,7 +11209,7 @@
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B17/$B$29)</f>
-        <v>0.0188679245283019</v>
+        <v>0.01875</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11159,7 +11222,7 @@
       </c>
       <c r="C18" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B18/$B$29)</f>
-        <v>0.00628930817610063</v>
+        <v>0.00625</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11172,7 +11235,7 @@
       </c>
       <c r="C19" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B19/$B$29)</f>
-        <v>0.00628930817610063</v>
+        <v>0.00625</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11185,7 +11248,7 @@
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B20/$B$29)</f>
-        <v>0.0943396226415094</v>
+        <v>0.09375</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11198,7 +11261,7 @@
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B21/$B$29)</f>
-        <v>0.0440251572327044</v>
+        <v>0.04375</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11211,7 +11274,7 @@
       </c>
       <c r="C22" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B22/$B$29)</f>
-        <v>0.00628930817610063</v>
+        <v>0.00625</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11224,7 +11287,7 @@
       </c>
       <c r="C23" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B23/$B$29)</f>
-        <v>0.0440251572327044</v>
+        <v>0.04375</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11237,7 +11300,7 @@
       </c>
       <c r="C24" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B24/$B$29)</f>
-        <v>0.0817610062893082</v>
+        <v>0.08125</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11250,7 +11313,7 @@
       </c>
       <c r="C25" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B25/$B$29)</f>
-        <v>0.0377358490566038</v>
+        <v>0.0375</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11263,7 +11326,7 @@
       </c>
       <c r="C26" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B26/$B$29)</f>
-        <v>0.0188679245283019</v>
+        <v>0.01875</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11276,7 +11339,7 @@
       </c>
       <c r="C27" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B27/$B$29)</f>
-        <v>0.0125786163522013</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11285,20 +11348,20 @@
       </c>
       <c r="B28" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A28)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B28/$B$29)</f>
-        <v>0.0251572327044025</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="B29" s="11" t="n">
         <f aca="false">COUNTA(Catálogo!$B$4:$B$1000)</f>
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">IF(B29=0,0,B29/B29)</f>
@@ -11308,12 +11371,12 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="B32" s="15" t="str">
         <f aca="false">IF(SUM(B3:B28)=B29,"OK","Existe AREA nova - adicionar linha no resumo")</f>
@@ -11349,64 +11412,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1106</v>
+        <v>1113</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1109</v>
+        <v>1116</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1110</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>1111</v>
+        <v>1118</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1112</v>
+        <v>1119</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1113</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>1114</v>
+        <v>1121</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
     </row>
   </sheetData>
@@ -11437,56 +11500,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>1118</v>
+        <v>1125</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>1119</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>1120</v>
+        <v>1127</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>1123</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>1126</v>
+        <v>1133</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>1127</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>1128</v>
+        <v>1135</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>1129</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11495,18 +11558,18 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>1130</v>
+        <v>1137</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>1131</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>1133</v>
+        <v>1140</v>
       </c>
     </row>
   </sheetData>

--- a/RC_Catalogo_Questionarios.xlsx
+++ b/RC_Catalogo_Questionarios.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="1141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="1154">
   <si>
     <t xml:space="preserve">RC · Catálogo de Questionários — Ricardina Correia · OPP 8233</t>
   </si>
@@ -3329,6 +3329,45 @@
   </si>
   <si>
     <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/Prova_Cuidar_Integridade_Corpo_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSAS — Escala de Ansiedade de Separação para Crianças (Criança)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8–11 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autorrelato de sintomas de ansiedade de separação (20 itens, 4 fatores). Corte total ≥ 68 orientativo (norma espanhola, não portuguesa; Méndez et al., 2014).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preocupação com a separação (cognitivo); Mal-estar da separação (psicofisiológico); Oposição à separação (comportamental); Calma na separação (fator positivo, invertido no cálculo — itens 3, 8, 12, 15, 19); Total (20–100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">csas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_csas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/CSAS_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSAS-P — Escala de Ansiedade de Separação para Crianças · Versão Pais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heterorrelato parental de ansiedade de separação (20 itens, 4 fatores). Sem ponto de corte; leitura principal por fator (z vs norma parental espanhola, não portuguesa; Méndez et al., 2022).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preocupação; Oposição; Calma (fator positivo/protetor — leitura inversa); Mal-estar (norma com efeito de chão — ler com cautela); Total orientativo = Preocupação + Oposição + Mal-estar + (30 − Calma)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">csas_p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_csas_p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/CSAS_P_v1.html</t>
   </si>
   <si>
     <t xml:space="preserve">Resumo por Área Clínica (recalcula automaticamente)</t>
@@ -3812,8 +3851,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M163" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A3:M163"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M165" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A3:M165"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nº"/>
     <tableColumn id="2" name="Nome do Instrumento"/>
@@ -4012,7 +4051,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M165"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -10818,6 +10857,90 @@
       </c>
       <c r="M163" s="7" t="s">
         <v>1101</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>161</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H164" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I164" s="6" t="s">
+        <v>1104</v>
+      </c>
+      <c r="J164" s="6" t="s">
+        <v>1105</v>
+      </c>
+      <c r="K164" s="6" t="s">
+        <v>1106</v>
+      </c>
+      <c r="L164" s="6" t="s">
+        <v>1107</v>
+      </c>
+      <c r="M164" s="7" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>162</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F165" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H165" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I165" s="6" t="s">
+        <v>1110</v>
+      </c>
+      <c r="J165" s="6" t="s">
+        <v>1111</v>
+      </c>
+      <c r="K165" s="6" t="s">
+        <v>1112</v>
+      </c>
+      <c r="L165" s="6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="M165" s="7" t="s">
+        <v>1114</v>
       </c>
     </row>
   </sheetData>
@@ -11001,7 +11124,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1102</v>
+        <v>1115</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11011,10 +11134,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1103</v>
+        <v>1116</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1104</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11027,7 +11150,7 @@
       </c>
       <c r="C3" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B3/$B$29)</f>
-        <v>0.0375</v>
+        <v>0.037037037037037</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11040,7 +11163,7 @@
       </c>
       <c r="C4" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B4/$B$29)</f>
-        <v>0.01875</v>
+        <v>0.0185185185185185</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11049,11 +11172,11 @@
       </c>
       <c r="B5" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A5)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B5/$B$29)</f>
-        <v>0.1</v>
+        <v>0.111111111111111</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11066,7 +11189,7 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B6/$B$29)</f>
-        <v>0.0875</v>
+        <v>0.0864197530864198</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11079,7 +11202,7 @@
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B7/$B$29)</f>
-        <v>0.0375</v>
+        <v>0.037037037037037</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11092,7 +11215,7 @@
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B8/$B$29)</f>
-        <v>0.025</v>
+        <v>0.0246913580246914</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11105,7 +11228,7 @@
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B9/$B$29)</f>
-        <v>0.0125</v>
+        <v>0.0123456790123457</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11118,7 +11241,7 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B10/$B$29)</f>
-        <v>0.00625</v>
+        <v>0.00617283950617284</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11131,7 +11254,7 @@
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B11/$B$29)</f>
-        <v>0.025</v>
+        <v>0.0246913580246914</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11144,7 +11267,7 @@
       </c>
       <c r="C12" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B12/$B$29)</f>
-        <v>0.075</v>
+        <v>0.0740740740740741</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11157,7 +11280,7 @@
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B13/$B$29)</f>
-        <v>0.05625</v>
+        <v>0.0555555555555556</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11170,7 +11293,7 @@
       </c>
       <c r="C14" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B14/$B$29)</f>
-        <v>0.1</v>
+        <v>0.0987654320987654</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11183,7 +11306,7 @@
       </c>
       <c r="C15" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B15/$B$29)</f>
-        <v>0.00625</v>
+        <v>0.00617283950617284</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11196,7 +11319,7 @@
       </c>
       <c r="C16" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B16/$B$29)</f>
-        <v>0.0125</v>
+        <v>0.0123456790123457</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11209,7 +11332,7 @@
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B17/$B$29)</f>
-        <v>0.01875</v>
+        <v>0.0185185185185185</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11222,7 +11345,7 @@
       </c>
       <c r="C18" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B18/$B$29)</f>
-        <v>0.00625</v>
+        <v>0.00617283950617284</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11235,7 +11358,7 @@
       </c>
       <c r="C19" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B19/$B$29)</f>
-        <v>0.00625</v>
+        <v>0.00617283950617284</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11248,7 +11371,7 @@
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B20/$B$29)</f>
-        <v>0.09375</v>
+        <v>0.0925925925925926</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11261,7 +11384,7 @@
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B21/$B$29)</f>
-        <v>0.04375</v>
+        <v>0.0432098765432099</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11274,7 +11397,7 @@
       </c>
       <c r="C22" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B22/$B$29)</f>
-        <v>0.00625</v>
+        <v>0.00617283950617284</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11287,7 +11410,7 @@
       </c>
       <c r="C23" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B23/$B$29)</f>
-        <v>0.04375</v>
+        <v>0.0432098765432099</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11300,7 +11423,7 @@
       </c>
       <c r="C24" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B24/$B$29)</f>
-        <v>0.08125</v>
+        <v>0.0802469135802469</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11313,7 +11436,7 @@
       </c>
       <c r="C25" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B25/$B$29)</f>
-        <v>0.0375</v>
+        <v>0.037037037037037</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11326,7 +11449,7 @@
       </c>
       <c r="C26" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B26/$B$29)</f>
-        <v>0.01875</v>
+        <v>0.0185185185185185</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11339,7 +11462,7 @@
       </c>
       <c r="C27" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B27/$B$29)</f>
-        <v>0.0125</v>
+        <v>0.0123456790123457</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11352,16 +11475,16 @@
       </c>
       <c r="C28" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B28/$B$29)</f>
-        <v>0.03125</v>
+        <v>0.0308641975308642</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>1105</v>
+        <v>1118</v>
       </c>
       <c r="B29" s="11" t="n">
         <f aca="false">COUNTA(Catálogo!$B$4:$B$1000)</f>
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">IF(B29=0,0,B29/B29)</f>
@@ -11371,12 +11494,12 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>1106</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>1107</v>
+        <v>1120</v>
       </c>
       <c r="B32" s="15" t="str">
         <f aca="false">IF(SUM(B3:B28)=B29,"OK","Existe AREA nova - adicionar linha no resumo")</f>
@@ -11412,64 +11535,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1108</v>
+        <v>1121</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>1109</v>
+        <v>1122</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1110</v>
+        <v>1123</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1111</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>1112</v>
+        <v>1125</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1113</v>
+        <v>1126</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1114</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>1115</v>
+        <v>1128</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1116</v>
+        <v>1129</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1117</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>1118</v>
+        <v>1131</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1119</v>
+        <v>1132</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1120</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1122</v>
+        <v>1135</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1123</v>
+        <v>1136</v>
       </c>
     </row>
   </sheetData>
@@ -11500,56 +11623,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1124</v>
+        <v>1137</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>1125</v>
+        <v>1138</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>1126</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>1127</v>
+        <v>1140</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>1128</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>1129</v>
+        <v>1142</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>1130</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>1131</v>
+        <v>1144</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1132</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>1133</v>
+        <v>1146</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>1134</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>1135</v>
+        <v>1148</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>1136</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11558,18 +11681,18 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>1137</v>
+        <v>1150</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>1138</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>1139</v>
+        <v>1152</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>1140</v>
+        <v>1153</v>
       </c>
     </row>
   </sheetData>

--- a/RC_Catalogo_Questionarios.xlsx
+++ b/RC_Catalogo_Questionarios.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="1154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="1173">
   <si>
     <t xml:space="preserve">RC · Catálogo de Questionários — Ricardina Correia · OPP 8233</t>
   </si>
@@ -3368,6 +3368,63 @@
   </si>
   <si>
     <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/CSAS_P_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGRS — Sohn Grayson Rating Scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mãe, Pai, Enc. Educação, Professor(a), Educador(a), Psicóloga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rastreio e sistematização da observação de comportamentos associados a PEA de alto funcionamento (Sohn &amp; Grayson, 2005). 58 itens · 6 domínios · Likert 1–4 (1 = Não é verdade · 2 = Raramente · 3 = Às vezes · 4 = Frequentemente) · SEM itens invertidos · amplitude 58–232 (o mínimo é 58 e não 0). Admite pais, professor e clínico em paralelo — o painel calcula a concordância inter-informantes (amplitude entre médias/item: ≥1,00 discrepância assinalável · ≥0,50 ligeira). Total bruto só é válido com 58/58 itens; com omissos apresenta estimativa prorrateada (média/item × 58), rotulada como exploratória. NÃO existem normas portuguesas — versão portuguesa é tradução de trabalho, sem adaptação transcultural nem validação psicométrica. Bandas globais dos autores (58–89 Muito baixa · 90–118 Baixa · 119–149 Média a moderada · 150–177 Moderada a alta · 178–207 Alta a muito alta · 208–232 Muito alta), sem derivação empírica publicada nem estudos independentes de fidelidade/validade/sensibilidade/especificidade. Classificação por domínio = convenção descritiva sem base normativa (média/item: 1,00–1,74 mínima · 1,75–2,49 ligeira · 2,50–3,24 moderada · 3,25–4,00 elevada) — PENDENTE DE RATIFICAÇÃO. Instrumento de rastreio: não estabelece nem exclui diagnóstico de PEA e não substitui avaliação diagnóstica multimodal. Terminologia original («Síndrome de Asperger», «PDD de alto funcionamento») é anterior ao DSM-5-TR/CID-11 — reportar em nomenclatura atual (PEA com especificadores de gravidade). Cautelas: Discurso e Linguagem pesa 38 % dos itens (22/58); Comportamento Motor tem só 2 itens (média instável); itens G02 (memorização) e L13 (vocabulário) descrevem competências mas são cotados na mesma direção.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comportamento Social (14 itens; 14–56) — amizades, iniciativa de jogo, jogo imaginativo e repetitivo, contacto ocular, expressões faciais/linguagem corporal, multidões, perspetiva do outro, compreensão e expressão emocional, espaço pessoal, regras de jogo; Comportamento (8 itens; 8–32) — medos incomuns, interesses obsessivos/ritualismo, pensamento dicotómico, hábitos alimentares, comportamentos persistentes, rigidez a mudanças/transições, perfecionismo, ansiedade; Discurso e Linguagem (22 itens; 22–88) — uso peculiar de palavras, não pedir explicação/ajuda, humor e provocações, iniciar e manter conversa recíproca, interesse pelo outro, discurso adultificado, comentários embaraçosos, perguntas e tópicos obsessivos, vocabulário, linguagem social, pronomes, prosódia/volume, linguagem em scripts, literalidade, ideia principal, rituais verbais, gestos, manutenção do tópico; Cognição (7 itens; 7–28) — conceitos abstratos, memorização, motricidade fina, literalidade do comportamento dos outros, generalização da aprendizagem, distratibilidade, atenção sustentada; Perceção Sensorial (5 itens; 5–20) — sensibilidade invulgar a ruídos, cheiros, paladares, texturas e toque; Comportamento Motor (2 itens; 2–8) — movimentos repetidos/estereotipados, dificuldades motoras; Pontuação Global (58–232) — bandas de probabilidade dos autores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sgrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_sgrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/SGRS_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIS-8 — Escala de Insónia de Atenas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rastreio de insónia clinicamente significativa e monitorização da evolução (Soldatos, Dikeos &amp; Paparrigopoulos, 2000, 2003). Autorrelato, 8 itens, escala ordinal 0–3, período de referência: último mês. Estrutura em dois blocos: itens 1–5 sono noturno (AIS-5) e itens 6–8 consequências diurnas. Todos os itens directos — sem itens invertidos e sem ponderações; total = soma dos 8 itens (0–24). Ponto de corte total ≥ 6 (sensibilidade 93%, especificidade 85%, 90% de classificação correta; regressão logística contra diagnóstico CID-10 de insónia não orgânica, amostra clínica adulta grega — NÃO validado em adolescentes). Bandas descritivas de gravidade de Okajima et al. (2020), critério ISI, amostra comunitária adulta japonesa — estatuto descritivo/exploratório. NÃO existem normas portuguesas e a formulação PT-PT dos itens não corresponde a uma versão portuguesa validada: comparações com dados normativos internacionais exigem reserva. Instrumento de rastreio e monitorização — não estabelece diagnóstico isoladamente: um resultado abaixo do ponto de corte não exclui perturbação do sono e um resultado acima não a confirma. Em adolescentes, integrar sempre com hábitos, rotinas e higiene do sono, ansiedade e ruminação pré-sono, impacto escolar e emocional, e discrepâncias pais ↔ autorrelato; quando indicado, complementar com diário de sono e avaliação médica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Índice noturno — AIS-5 (itens 1–5; 0–15) — sintomatologia noturna: dificuldade em adormecer (indução), despertares durante a noite (manutenção), acordar mais cedo do que desejado (despertar final), duração total do sono e qualidade global do sono; Índice diurno (itens 6–8; 0–9) — repercussão diurna: sensação de bem-estar durante o dia, funcionamento diário (atenção, energia, desempenho) e sonolência durante o dia; Total AIS-8 (0–24) — soma directa dos 8 itens; Banda descritiva de gravidade — 0–5 Ausência de insónia · 6–9 Insónia ligeira · 10–15 Insónia moderada · 16–24 Insónia grave (Okajima et al., 2020; leitura exploratória em adolescentes); Rastreio (ponto de corte ≥ 6) — positivo/negativo face ao ponto de corte de Soldatos et al. (2003). Indicadores auxiliares descritivos, sem estatuto diagnóstico: nº de itens com resposta ≥ 2 (extensão da sintomatologia) e nº de itens com resposta = 3 (intensidade máxima referida); perfil dimensional por comparação da % do máximo entre índice noturno e índice diurno (diferença ≥ 20 pontos percentuais = predomínio relativo).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ais8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_ais8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/AIS_8_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAD-7 — Escala de Ansiedade Generalizada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rastreio da gravidade sintomática de ansiedade generalizada e monitorização da evolução (Spitzer, Kroenke, Williams &amp; Löwe, 2006). Autorrelato, 7 itens, escala ordinal 0–3, período de referência: últimos 14 dias; aplicação individual ou coletiva em 2–3 minutos; heteroaplicação admissível em caso de limitação de literacia, registando-se essa condição. Instrumento UNIDIMENSIONAL: total = soma directa dos 7 itens (0–21), sem subescalas, sem itens invertidos e sem ponderações (ACP em Sousa et al., 2015; AFE em Leite &amp; Faro, 2022, 62,8% de variância explicada) — os agrupamentos de conteúdo são meramente descritivos e não têm estatuto psicométrico. Ponto de corte operacional ≥ 10 (Spitzer et al., 2006: sensibilidade 89%, especificidade 82%). Bandas de gravidade descritiva 0–4 · 5–9 · 10–14 · 15–21 da amostra original norte-americana, replicadas na literatura subsequente. NÃO EXISTEM NORMAS PORTUGUESAS (percentis ou pontuações padronizadas): os limiares 5/10/15 são bandas descritivas e não limiares diagnósticos — «Ansiedade grave» descreve intensidade sintomática, não é atribuição nosológica. A validação portuguesa de referência (Sousa et al., 2015; artigo em acesso aberto CC-BY) foi conduzida em amostra clínica psiquiátrica adulta (78,8% mulheres, idade média 52,2 anos) — a generalização a populações não clínicas, a outros escalões etários e a contexto pediátrico exige prudência; Gonçalves (2019, validação portuguesa 6–16 anos) reporta prevalência com base num valor superior a 11, não coincidente com o corte adulto de 10. Instrumento de RASTREIO: não constitui, por si, instrumento de diagnóstico e não substitui a entrevista clínica nem o exame do estado mental — um total elevado é inespecífico e sobrepõe-se a sintomatologia depressiva (r = 0,450 com a subescala de depressão da HADS) e um total baixo não exclui perturbação de ansiedade. Estatuto de acesso: VIA A — instrumento legalmente acessível, reproduzido com atribuição (família PHQ/GAD, autorização expressa de reprodução, tradução e distribuição).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total GAD-7 (0–21) — soma directa dos 7 itens; instrumento unidimensional, NÃO calcula subescalas. Banda de gravidade descritiva — 0–4 Ansiedade mínima (sintomatologia ansiosa ausente ou residual no período de referência) · 5–9 Ansiedade leve (intensidade ligeira, abaixo do limiar de rastreio) · 10–14 Ansiedade moderada (intensidade moderada, acima do limiar de rastreio) · 15–21 Ansiedade grave (intensidade elevada, acima do limiar de rastreio) — limiares de Spitzer et al. (2006), NÃO são normas portuguesas. Rastreio (ponto de corte ≥ 10) — positivo/negativo face ao ponto de corte operacional, editável. Validade do protocolo — regra de dados em falta (decisão interna documentada; a escala original não a define): itens não respondidos são excluídos do denominador e NUNCA cotados como zero (0 é resposta substantiva, «Nunca»); com 6 itens respondidos o total é estimado por prorata — ARRED(soma ÷ n × 7; 0) — e sinalizado como estimativa; com menos de 6 o protocolo é inválido e não é gerada interpretação. Indicadores auxiliares descritivos, sem estatuto diagnóstico: % da pontuação máxima; nº de itens com pontuação ≥ 2 (sintoma referido em mais de metade dos dias); item de pontuação mais elevada (o primeiro, em caso de empate). Agrupamentos de conteúdo MERAMENTE DESCRITIVOS (sem estatuto de subescala; sem cotação própria): apreensão/tensão nervosa (item 1); cognitivo — incontrolabilidade da preocupação (item 2); cognitivo — preocupação excessiva e multifocal (item 3); somático — tensão/dificuldade de relaxamento (item 4); somático-motor — inquietação (item 5); irritabilidade (item 6); apreensão antecipatória (item 7). Nota: a versão em uso omite o item 8 canónico (dificuldade causada pelos problemas), que não é cotado mas informa a apreciação da incapacidade funcional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gad7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_gad7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/GAD7_v1.html</t>
   </si>
   <si>
     <t xml:space="preserve">Resumo por Área Clínica (recalcula automaticamente)</t>
@@ -3851,8 +3908,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M165" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A3:M165"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M168" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A3:M168"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nº"/>
     <tableColumn id="2" name="Nome do Instrumento"/>
@@ -4051,7 +4108,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M165"/>
+  <dimension ref="A1:M168"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -10859,7 +10916,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="5" t="n">
         <f aca="false">ROW()-3</f>
         <v>161</v>
@@ -10901,7 +10958,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="5" t="n">
         <f aca="false">ROW()-3</f>
         <v>162</v>
@@ -10941,6 +10998,132 @@
       </c>
       <c r="M165" s="7" t="s">
         <v>1114</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A166" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>163</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="F166" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H166" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I166" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="J166" s="6" t="s">
+        <v>1118</v>
+      </c>
+      <c r="K166" s="6" t="s">
+        <v>1119</v>
+      </c>
+      <c r="L166" s="6" t="s">
+        <v>1120</v>
+      </c>
+      <c r="M166" s="7" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A167" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>164</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="F167" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H167" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I167" s="6" t="s">
+        <v>1123</v>
+      </c>
+      <c r="J167" s="6" t="s">
+        <v>1124</v>
+      </c>
+      <c r="K167" s="6" t="s">
+        <v>1125</v>
+      </c>
+      <c r="L167" s="6" t="s">
+        <v>1126</v>
+      </c>
+      <c r="M167" s="7" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A168" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>165</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E168" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="F168" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H168" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I168" s="6" t="s">
+        <v>1129</v>
+      </c>
+      <c r="J168" s="6" t="s">
+        <v>1130</v>
+      </c>
+      <c r="K168" s="6" t="s">
+        <v>1131</v>
+      </c>
+      <c r="L168" s="6" t="s">
+        <v>1132</v>
+      </c>
+      <c r="M168" s="7" t="s">
+        <v>1133</v>
       </c>
     </row>
   </sheetData>
@@ -11124,7 +11307,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1115</v>
+        <v>1134</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11134,10 +11317,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1116</v>
+        <v>1135</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1117</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11150,7 +11333,7 @@
       </c>
       <c r="C3" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B3/$B$29)</f>
-        <v>0.037037037037037</v>
+        <v>0.0363636363636364</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11163,7 +11346,7 @@
       </c>
       <c r="C4" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B4/$B$29)</f>
-        <v>0.0185185185185185</v>
+        <v>0.0181818181818182</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11172,11 +11355,11 @@
       </c>
       <c r="B5" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A5)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B5/$B$29)</f>
-        <v>0.111111111111111</v>
+        <v>0.115151515151515</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11189,7 +11372,7 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B6/$B$29)</f>
-        <v>0.0864197530864198</v>
+        <v>0.0848484848484849</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11202,7 +11385,7 @@
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B7/$B$29)</f>
-        <v>0.037037037037037</v>
+        <v>0.0363636363636364</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11215,7 +11398,7 @@
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B8/$B$29)</f>
-        <v>0.0246913580246914</v>
+        <v>0.0242424242424242</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11228,7 +11411,7 @@
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B9/$B$29)</f>
-        <v>0.0123456790123457</v>
+        <v>0.0121212121212121</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11241,7 +11424,7 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B10/$B$29)</f>
-        <v>0.00617283950617284</v>
+        <v>0.00606060606060606</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11254,7 +11437,7 @@
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B11/$B$29)</f>
-        <v>0.0246913580246914</v>
+        <v>0.0242424242424242</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11267,7 +11450,7 @@
       </c>
       <c r="C12" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B12/$B$29)</f>
-        <v>0.0740740740740741</v>
+        <v>0.0727272727272727</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11280,7 +11463,7 @@
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B13/$B$29)</f>
-        <v>0.0555555555555556</v>
+        <v>0.0545454545454545</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11293,7 +11476,7 @@
       </c>
       <c r="C14" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B14/$B$29)</f>
-        <v>0.0987654320987654</v>
+        <v>0.096969696969697</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11306,7 +11489,7 @@
       </c>
       <c r="C15" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B15/$B$29)</f>
-        <v>0.00617283950617284</v>
+        <v>0.00606060606060606</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11319,7 +11502,7 @@
       </c>
       <c r="C16" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B16/$B$29)</f>
-        <v>0.0123456790123457</v>
+        <v>0.0121212121212121</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11332,7 +11515,7 @@
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B17/$B$29)</f>
-        <v>0.0185185185185185</v>
+        <v>0.0181818181818182</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11345,7 +11528,7 @@
       </c>
       <c r="C18" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B18/$B$29)</f>
-        <v>0.00617283950617284</v>
+        <v>0.00606060606060606</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11358,7 +11541,7 @@
       </c>
       <c r="C19" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B19/$B$29)</f>
-        <v>0.00617283950617284</v>
+        <v>0.00606060606060606</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11367,11 +11550,11 @@
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A20)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B20/$B$29)</f>
-        <v>0.0925925925925926</v>
+        <v>0.096969696969697</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11384,7 +11567,7 @@
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B21/$B$29)</f>
-        <v>0.0432098765432099</v>
+        <v>0.0424242424242424</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11397,7 +11580,7 @@
       </c>
       <c r="C22" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B22/$B$29)</f>
-        <v>0.00617283950617284</v>
+        <v>0.00606060606060606</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11410,7 +11593,7 @@
       </c>
       <c r="C23" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B23/$B$29)</f>
-        <v>0.0432098765432099</v>
+        <v>0.0424242424242424</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11423,7 +11606,7 @@
       </c>
       <c r="C24" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B24/$B$29)</f>
-        <v>0.0802469135802469</v>
+        <v>0.0787878787878788</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11436,7 +11619,7 @@
       </c>
       <c r="C25" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B25/$B$29)</f>
-        <v>0.037037037037037</v>
+        <v>0.0363636363636364</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11449,7 +11632,7 @@
       </c>
       <c r="C26" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B26/$B$29)</f>
-        <v>0.0185185185185185</v>
+        <v>0.0181818181818182</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11458,11 +11641,11 @@
       </c>
       <c r="B27" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A27)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B27/$B$29)</f>
-        <v>0.0123456790123457</v>
+        <v>0.0181818181818182</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11475,16 +11658,16 @@
       </c>
       <c r="C28" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B28/$B$29)</f>
-        <v>0.0308641975308642</v>
+        <v>0.0303030303030303</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>1118</v>
+        <v>1137</v>
       </c>
       <c r="B29" s="11" t="n">
         <f aca="false">COUNTA(Catálogo!$B$4:$B$1000)</f>
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">IF(B29=0,0,B29/B29)</f>
@@ -11494,12 +11677,12 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>1119</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>1120</v>
+        <v>1139</v>
       </c>
       <c r="B32" s="15" t="str">
         <f aca="false">IF(SUM(B3:B28)=B29,"OK","Existe AREA nova - adicionar linha no resumo")</f>
@@ -11535,64 +11718,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1121</v>
+        <v>1140</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>1122</v>
+        <v>1141</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1123</v>
+        <v>1142</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1124</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>1125</v>
+        <v>1144</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1126</v>
+        <v>1145</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1127</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>1128</v>
+        <v>1147</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1129</v>
+        <v>1148</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1130</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>1131</v>
+        <v>1150</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1132</v>
+        <v>1151</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1133</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1135</v>
+        <v>1154</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1136</v>
+        <v>1155</v>
       </c>
     </row>
   </sheetData>
@@ -11623,56 +11806,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1137</v>
+        <v>1156</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>1138</v>
+        <v>1157</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>1139</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>1140</v>
+        <v>1159</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>1141</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>1142</v>
+        <v>1161</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>1143</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>1144</v>
+        <v>1163</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1145</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>1146</v>
+        <v>1165</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>1147</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>1148</v>
+        <v>1167</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>1149</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11681,18 +11864,18 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>1150</v>
+        <v>1169</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>1151</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>1152</v>
+        <v>1171</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>1153</v>
+        <v>1172</v>
       </c>
     </row>
   </sheetData>

--- a/RC_Catalogo_Questionarios.xlsx
+++ b/RC_Catalogo_Questionarios.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="1173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="1199">
   <si>
     <t xml:space="preserve">RC · Catálogo de Questionários — Ricardina Correia · OPP 8233</t>
   </si>
@@ -3425,6 +3425,84 @@
   </si>
   <si>
     <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/GAD7_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMQ — Questionário de Mutismo Seletivo (Pais)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantificação da frequência de fala por contexto, da interferência funcional associada e monitorização da mudança em resposta a intervenção (Bergman, Keller, Piacentini &amp; Bergman, 2008). Relato parental, 23 itens. Itens 1–17: escala ordinal de frequência 0–3 (Nunca · Raramente · Frequentemente · Sempre), período de referência: últimas duas semanas; itens 18–23: escala de interferência/desconforto 0–3 (Nada · Um pouco · Moderadamente · Muito), que NÃO integra a pontuação de sintomas. ATENÇÃO — ESCALA INVERSA: pontuações mais BAIXAS indicam MENOR frequência de fala e, portanto, MAIOR gravidade sintomática. Métrica primária: média por escala (0–3); métrica secundária: soma prorrateada (média × nº nominal de itens). Os itens 12 e 17 admitem legitimamente «Não aplicável» (ausência de ama/cuidador; ausência de atividades extraescolares) e são excluídos de numerador e denominador. NÃO é instrumento de diagnóstico e não gera pontos de corte diagnósticos; não existem normas portuguesas — todos os limiares utilizados são exploratórios. Não discrimina de forma fiável o mutismo seletivo da perturbação de ansiedade social isolada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escola (itens 1–6; média 0–3; N mín. 5 de 6; referência DT ≥ 2,50) — frequência de fala com colegas, professores e perante a turma. · Casa/Família (itens 7–12; N mín. 4 de 6; referência DT ≥ 2,50) — fala com familiares coabitantes e não coabitantes, ao telefone e com cuidadores; é estruturalmente a subescala menos afetada, pelo que valores baixos exigem reformulação da hipótese. · Social (itens 13–17; N mín. 3 de 5; referência DT ≈ 2,00, estruturalmente MAIS BAIXA — comparar contra 2,50 produziria sobreidentificação sistemática) — fala com desconhecidos, profissionais de saúde, funcionários e em atividades extraescolares. · TOTAL SMQ (itens 1–17; N mín. 13 de 17; invalidado se qualquer subescala não for cotada). · Escala de sintomas em métrica de soma (0–51) — rastreio: ≤ 14 positivo com especificidade máxima · ≤ 38 positivo (sensibilidade 100%, especificidade 74,3%) · &gt; 38 negativo. ADVERTÊNCIA: o corte de 13 citado na literatura secundária refere-se à cotação INVERTIDA do estudo neerlandês e NÃO se aplica à cotação original — o equivalente correto é 38. · Interferência funcional na criança (itens 18–21; N mín. 3 de 4). · Desconforto da criança (item 22). · Desconforto do cuidador (item 23). · Índice global de interferência (itens 18–23; soma 0–18; escala autónoma, α = 0,81). · IDC — Índice de Discrepância Contextual (média Casa/Família − média Escola; construção própria; interpretável apenas com média Escola &lt; 2,00; a classificação «Restrição extensiva ao contexto familiar» com média Casa &lt; 1,50 tem precedência sobre a magnitude do IDC). · Discrepância Social − Escola. · Concordância inter-informante na subescala Escola (calculada automaticamente a partir da versão Professores do mesmo código: &lt; 0,50 elevada · 0,50–0,99 moderada · ≥ 1,00 discrepância relevante). Bandas descritivas da média (0–3): 0–0,49 Fala ausente ou quase ausente · 0,50–0,99 Fala muito reduzida · 1,00–1,49 Fala reduzida · 1,50–1,99 Fala inconsistente · 2,00–2,49 Fala frequente · 2,50–3,00 Fala consistente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smq_pais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_smq_pais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/SMQ_Pais_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMQ — Questionário de Mutismo Seletivo (Professores)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantificação da frequência de fala do aluno em contexto escolar e da interferência percebida pelo professor, com utilização preferencial na monitorização da mudança (Bergman, Keller, Piacentini &amp; Bergman, 2008). Relato do professor/educador, 11 itens. Itens 1–6: escala ordinal de frequência 0–3 (Nunca · Raramente · Frequentemente · Sempre), período de referência: últimas duas semanas — conteúdos item a item idênticos aos itens 1–6 da versão parental, o que torna a comparação inter-informante metodologicamente limpa; itens a–e: escala de interferência/desconforto 0–3. ATENÇÃO — ESCALA INVERSA: pontuações mais BAIXAS indicam MENOR frequência de fala e MAIOR gravidade. LIMITE DE ALCANCE: esta versão contém 6 itens de frequência e 5 de interferência, diferindo do School Speech Questionnaire publicado — os resultados das duas versões NÃO são permutáveis, e o rastreio por métrica de soma (≤ 38/51) aplica-se exclusivamente à versão parental de 17 itens. Sozinha não estabelece o padrão situacional que define o mutismo seletivo (Critério A do DSM-5-TR), por observar um único contexto: exige a versão parental ao lado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escola — professor (itens 1–6; média 0–3; soma prorrateada 0–18; N mín. 5 de 6; referência DT ≥ 2,50, aplicada por analogia à cotação escolar por professor) — fala com colegas próximos e com a maioria dos colegas, resposta a questões do professor, iniciativa de questionar, fala com professores e funcionários, e fala em grupo ou perante a turma. Âncoras clínicos: nas amostras clínicas de mutismo seletivo os valores de base situam-se consistentemente abaixo de 1,00 e, após intervenção, tipicamente entre 1 e 2; Bergman et al. (2008) reportaram valores ≥ 2,50 num pequeno grupo referenciado por outras perturbações de ansiedade (n = 18), o que sustenta a especificidade desta subescala. · Interferência funcional percebida (itens a–c; N mín. 2 de 3) — interferência na escola, nas situações sociais e na vida do aluno em geral. · Desconforto do aluno (item d). · Desconforto do próprio professor (item e) — reportado separadamente por não constituir o mesmo constructo. · Concordância inter-informante na subescala Escola (calculada automaticamente a partir da versão Pais do mesmo código; o professor observa o contexto diretamente, o relato parental sobre a escola é indireto: &lt; 0,50 concordância elevada · 0,50–0,99 moderada · ≥ 1,00 discrepância relevante). NOTA: os itens de interferência NÃO são sobreponíveis entre versões (a parental tem 4 itens funcionais, incluindo relações familiares; esta tem 3), pelo que apenas a subescala Escola é comparada entre informantes. Bandas descritivas da média (0–3): 0–0,49 Fala ausente ou quase ausente · 0,50–0,99 Fala muito reduzida · 1,00–1,49 Fala reduzida · 1,50–1,99 Fala inconsistente · 2,00–2,49 Fala frequente · 2,50–3,00 Fala consistente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smq_prof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_smq_prof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/SMQ_Professores_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QCVE-P — Comportamento Verbal em Contexto Escolar (Professor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professor(a), Educador(a), Diretor(a) de Turma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mede a frequência do comportamento verbal do/a aluno/a em contexto escolar, desagregada por interlocutor e por grau de exposição comunicativa, na avaliação e no seguimento do mutismo seletivo. Instrumento ORIGINAL de Ricardina Correia (2026), Via B, inspirado no modelo estrutural do School Speech Questionnaire (Bergman, Piacentini &amp; McCracken, 2002) — não é tradução nem adaptação autorizada, e não é permutável com o SMQ. Informante: docente com contacto regular. Janela: último mês. 8 a 12 minutos. ATENÇÃO: sem normas portuguesas — bandas exploratórias, de ancoragem analógica; instrumento de gravidade e de mudança, NÃO de diagnóstico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E1 — Comunicação verbal com pares (itens 1–4; média 0–3). E2 — Comunicação verbal com adultos da escola (itens 5–8; média 0–3). E3 — Comunicação verbal em situações de exposição (itens 9–12; média 0–3). Total ECV — média das três médias de subescala (0–3); ESCALA INVERSA: mais baixo = menos fala = maior gravidade; bandas 0,00–0,50 ausente ou vestigial · 0,51–1,00 muito restrito · 1,01–1,75 restrito · 1,76–2,49 parcialmente estabelecido · 2,50–3,00 ajustado ao contexto. IRV — Índice de Restrição Verbal (3 − Total ECV), orientado à gravidade. ICNV — Índice de Comunicação Não Verbal (itens 13–16; média 0–3), índice AUTÓNOMO, nunca somado à ECV. IIF — Índice de Interferência Funcional (itens 17–20; média 0–3), escala de direção INVERTIDA e índice AUTÓNOMO, nunca somado à ECV. Bloco contextual (Parte IV) não cotado, mas condicionante da validade da leitura. «SO» excluído do numerador e do denominador; subescala válida com ≥3 de 4 itens; com exactamente 3 marca estimativa exploratória; com ≤2 é INVÁLIDA e nunca cotada a zero.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qcvep_prof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_qcvep_prof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/QCVEP_Prof_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBQ-SF — Children’s Behavior Questionnaire (Forma Breve)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3–7 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avalia o temperamento infantil em 15 escalas e 3 dimensões, por hétero-relato do cuidador principal (94 itens, Likert 1–7 com opção NA). Sem normas portuguesas — leitura descritiva e ipsativa, sem valor diagnóstico autónomo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extroversão / Surgência (dimensão, Modelo A: NA + AE + EIP + IM + SG − TI). Afetividade Negativa (IF + DE + ME + TR − SLR). Controlo por Esforço (FA + CI + BIP + SP). Extroversão variante restrita, 4 escalas (Putnam &amp; Rothbart, 2006). Modelo B português (Lopes, 2011), complementar: Extroversão PT, Afetividade Negativa PT, Controlo por Esforço PT. 15 escalas: Nível de Atividade (7 itens); Irritação / Frustração (6); Aproximação / Entusiasmo (6); Foco Atencional (6); Desconforto (6); Sensibilidade / Limiar de Resposta (6); Medo (6); Elevada Intensidade de Prazer (6); Impulsividade (6); Controlo Inibido (6); Baixa Intensidade de Prazer (8); Sensibilidade Percetiva (6); Tristeza (7); Timidez (6); Sorrisos / Gargalhadas (6). Cotação por MÉDIA na métrica 1–7 (ponto neutro = 4); NA e omissos excluídos do denominador. SEM normas portuguesas: bandas descritivas, leitura preferencial por perfil ipsativo intraindividual.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cbqsf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_cbqsf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/CBQ_SF_v1.html</t>
   </si>
   <si>
     <t xml:space="preserve">Resumo por Área Clínica (recalcula automaticamente)</t>
@@ -3908,8 +3986,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M168" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A3:M168"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M172" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A3:M172"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nº"/>
     <tableColumn id="2" name="Nome do Instrumento"/>
@@ -4108,7 +4186,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M168"/>
+  <dimension ref="A1:M172"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -11124,6 +11202,174 @@
       </c>
       <c r="M168" s="7" t="s">
         <v>1133</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A169" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>166</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="F169" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H169" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I169" s="6" t="s">
+        <v>1135</v>
+      </c>
+      <c r="J169" s="6" t="s">
+        <v>1136</v>
+      </c>
+      <c r="K169" s="6" t="s">
+        <v>1137</v>
+      </c>
+      <c r="L169" s="6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="M169" s="7" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A170" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>167</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D170" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E170" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="F170" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H170" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I170" s="6" t="s">
+        <v>1141</v>
+      </c>
+      <c r="J170" s="6" t="s">
+        <v>1142</v>
+      </c>
+      <c r="K170" s="6" t="s">
+        <v>1143</v>
+      </c>
+      <c r="L170" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="M170" s="7" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A171" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>168</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="F171" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H171" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I171" s="6" t="s">
+        <v>1148</v>
+      </c>
+      <c r="J171" s="6" t="s">
+        <v>1149</v>
+      </c>
+      <c r="K171" s="6" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L171" s="6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="M171" s="7" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A172" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>169</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E172" s="6" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H172" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I172" s="6" t="s">
+        <v>1155</v>
+      </c>
+      <c r="J172" s="6" t="s">
+        <v>1156</v>
+      </c>
+      <c r="K172" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="L172" s="6" t="s">
+        <v>1158</v>
+      </c>
+      <c r="M172" s="7" t="s">
+        <v>1159</v>
       </c>
     </row>
   </sheetData>
@@ -11307,7 +11553,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1134</v>
+        <v>1160</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11317,10 +11563,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1135</v>
+        <v>1161</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1136</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11333,7 +11579,7 @@
       </c>
       <c r="C3" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B3/$B$29)</f>
-        <v>0.0363636363636364</v>
+        <v>0.0355029585798817</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11346,7 +11592,7 @@
       </c>
       <c r="C4" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B4/$B$29)</f>
-        <v>0.0181818181818182</v>
+        <v>0.0177514792899408</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11355,11 +11601,11 @@
       </c>
       <c r="B5" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A5)</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B5/$B$29)</f>
-        <v>0.115151515151515</v>
+        <v>0.130177514792899</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11372,7 +11618,7 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B6/$B$29)</f>
-        <v>0.0848484848484849</v>
+        <v>0.0828402366863905</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11385,7 +11631,7 @@
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B7/$B$29)</f>
-        <v>0.0363636363636364</v>
+        <v>0.0355029585798817</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11398,7 +11644,7 @@
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B8/$B$29)</f>
-        <v>0.0242424242424242</v>
+        <v>0.0236686390532544</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11411,7 +11657,7 @@
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B9/$B$29)</f>
-        <v>0.0121212121212121</v>
+        <v>0.0118343195266272</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11424,7 +11670,7 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B10/$B$29)</f>
-        <v>0.00606060606060606</v>
+        <v>0.00591715976331361</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11437,7 +11683,7 @@
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B11/$B$29)</f>
-        <v>0.0242424242424242</v>
+        <v>0.0236686390532544</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11450,7 +11696,7 @@
       </c>
       <c r="C12" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B12/$B$29)</f>
-        <v>0.0727272727272727</v>
+        <v>0.0710059171597633</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11463,7 +11709,7 @@
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B13/$B$29)</f>
-        <v>0.0545454545454545</v>
+        <v>0.0532544378698225</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11476,7 +11722,7 @@
       </c>
       <c r="C14" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B14/$B$29)</f>
-        <v>0.096969696969697</v>
+        <v>0.0946745562130178</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11489,7 +11735,7 @@
       </c>
       <c r="C15" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B15/$B$29)</f>
-        <v>0.00606060606060606</v>
+        <v>0.00591715976331361</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11502,7 +11748,7 @@
       </c>
       <c r="C16" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B16/$B$29)</f>
-        <v>0.0121212121212121</v>
+        <v>0.0118343195266272</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11515,7 +11761,7 @@
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B17/$B$29)</f>
-        <v>0.0181818181818182</v>
+        <v>0.0177514792899408</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11528,7 +11774,7 @@
       </c>
       <c r="C18" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B18/$B$29)</f>
-        <v>0.00606060606060606</v>
+        <v>0.00591715976331361</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11541,7 +11787,7 @@
       </c>
       <c r="C19" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B19/$B$29)</f>
-        <v>0.00606060606060606</v>
+        <v>0.00591715976331361</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11554,7 +11800,7 @@
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B20/$B$29)</f>
-        <v>0.096969696969697</v>
+        <v>0.0946745562130178</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11567,7 +11813,7 @@
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B21/$B$29)</f>
-        <v>0.0424242424242424</v>
+        <v>0.0414201183431953</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11580,7 +11826,7 @@
       </c>
       <c r="C22" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B22/$B$29)</f>
-        <v>0.00606060606060606</v>
+        <v>0.00591715976331361</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11593,7 +11839,7 @@
       </c>
       <c r="C23" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B23/$B$29)</f>
-        <v>0.0424242424242424</v>
+        <v>0.0414201183431953</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11602,11 +11848,11 @@
       </c>
       <c r="B24" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A24)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C24" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B24/$B$29)</f>
-        <v>0.0787878787878788</v>
+        <v>0.0828402366863905</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11619,7 +11865,7 @@
       </c>
       <c r="C25" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B25/$B$29)</f>
-        <v>0.0363636363636364</v>
+        <v>0.0355029585798817</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11632,7 +11878,7 @@
       </c>
       <c r="C26" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B26/$B$29)</f>
-        <v>0.0181818181818182</v>
+        <v>0.0177514792899408</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11645,7 +11891,7 @@
       </c>
       <c r="C27" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B27/$B$29)</f>
-        <v>0.0181818181818182</v>
+        <v>0.0177514792899408</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11658,16 +11904,16 @@
       </c>
       <c r="C28" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B28/$B$29)</f>
-        <v>0.0303030303030303</v>
+        <v>0.029585798816568</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>1137</v>
+        <v>1163</v>
       </c>
       <c r="B29" s="11" t="n">
         <f aca="false">COUNTA(Catálogo!$B$4:$B$1000)</f>
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">IF(B29=0,0,B29/B29)</f>
@@ -11677,12 +11923,12 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="B32" s="15" t="str">
         <f aca="false">IF(SUM(B3:B28)=B29,"OK","Existe AREA nova - adicionar linha no resumo")</f>
@@ -11718,64 +11964,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1140</v>
+        <v>1166</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>1141</v>
+        <v>1167</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1142</v>
+        <v>1168</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1143</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1145</v>
+        <v>1171</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1146</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>1147</v>
+        <v>1173</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1148</v>
+        <v>1174</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1149</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>1150</v>
+        <v>1176</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1151</v>
+        <v>1177</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1152</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>1153</v>
+        <v>1179</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1154</v>
+        <v>1180</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1155</v>
+        <v>1181</v>
       </c>
     </row>
   </sheetData>
@@ -11806,56 +12052,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1156</v>
+        <v>1182</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>1157</v>
+        <v>1183</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>1158</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>1159</v>
+        <v>1185</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>1160</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>1161</v>
+        <v>1187</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>1162</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>1163</v>
+        <v>1189</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1164</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>1165</v>
+        <v>1191</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>1166</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>1167</v>
+        <v>1193</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>1168</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11864,18 +12110,18 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>1169</v>
+        <v>1195</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>1170</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>1171</v>
+        <v>1197</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>1172</v>
+        <v>1198</v>
       </c>
     </row>
   </sheetData>

--- a/RC_Catalogo_Questionarios.xlsx
+++ b/RC_Catalogo_Questionarios.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="1199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="1212">
   <si>
     <t xml:space="preserve">RC · Catálogo de Questionários — Ricardina Correia · OPP 8233</t>
   </si>
@@ -3503,6 +3503,45 @@
   </si>
   <si>
     <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/CBQ_SF_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QRF-C — Questionário de Relação Fraterna (Criança)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8–16 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descreve a perceção da criança sobre a relação com um irmão específico e sobre a parcialidade parental percebida (43 itens, autorrelato, métrica 1–5). Instrumento ORIGINAL de Ricardina Correia (Via B), inspirado no modelo estrutural de Furman &amp; Buhrmester (1985): NÃO é o SRQ, não é tradução do SRQ e não é equivalente ao SRQ. SEM aferição portuguesa e SEM estudo psicométrico próprio — não existem normas, percentis, pontuações T nem pontos de corte clínicos; todas as bandas são descritivas e ancoradas na métrica de resposta. Leituras válidas: discrepância intradiádica (os dois irmãos respondem sobre a mesma relação), discrepância entre informadores e medida repetida intraindividual. Uma aplicação = uma díade: com dois irmãos, atribuir dois protocolos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calor / Proximidade (dimensão: Companheirismo + Intimidade + Afeto e conduta prossocial + Admiração dirigida; exige 3 das 4 escalas). Conflito (Discussão + Antagonismo + Competição; exige 2 das 3). Estatuto / Poder relativo (diferencial com sinal preservado: média de Cuidado prestado e Dominância exercida menos média de Cuidado recebido e Dominância sofrida; amplitude −4 a +4, positivo = polo no próprio; exige as 4 escalas). Intensidade do estatuto (média das quatro escalas do bloco II). Rivalidade (máximo das magnitudes de parcialidade percebida; amplitude 0 a 2; média retida como auxiliar). Parcialidade percebida — Figura parental 1 (direção = média dos itens menos 3, amplitude −2 a +2; magnitude = valor absoluto). Parcialidade percebida — Figura parental 2 (idem). Configuração da parcialidade (sem parcialidade relevante / unifigural / bifigural). Assimetria interparental (direção Figura 1 menos direção Figura 2). Legitimidade do tratamento diferencial — Figura 1 (moderador autónomo, fora das dimensões). Legitimidade do tratamento diferencial — Figura 2 (idem). Satisfação com a relação fraterna (âncora avaliativa global). Importância atribuída à relação fraterna (âncora avaliativa global). Índices de controlo: invariância de resposta (desvio-padrão zero = protocolo não interpretável), variabilidade reduzida, tendência de resposta extrema e centralização no ponto médio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qrfc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_qrfc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/QRFC_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QCF-P — Questionário de Comportamento Fraterno (Parental)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descreve o comportamento observável de cada filho em relação aos irmãos e o tratamento diferencial relatado pelo progenitor (29 itens por filho, até 4 filhos descritos lado a lado no mesmo protocolo, métrica de frequência 1–5). Contrapartida parental do QRF-C. Instrumento ORIGINAL de Ricardina Correia (Via B), inspirado na estrutura de seis fatores do Sibling Inventory of Behavior: NÃO é o SIB, não é tradução do SIB e não é equivalente ao SIB. SEM aferição portuguesa e SEM estudo psicométrico próprio — não existem normas, percentis, pontuações T nem pontos de corte clínicos. NENHUM VALOR DESCREVE A QUALIDADE DO EXERCÍCIO PARENTAL: descreve o comportamento relatado dos filhos entre si e a estrutura da descrição feita por este informador. Um progenitor por protocolo: numa família com dois progenitores, uma ronda completa são dois protocolos, preenchidos separadamente e sem consulta mútua. Mínimo de dois filhos identificados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Companheirismo (itens 1–4). Empatia (5–8). Ensino / Tutoria (9–12). Rivalidade (13–16) — atenção: aqui designa comportamento rivalitário observado, e não a parcialidade parental percebida do QRF-C; a contrapartida real é a Competição (E11). Agressão (17–20). Evitamento (21–24) — sem contrapartida no QRF-C. Polo positivo e Polo negativo (índices auxiliares descritivos, não fatores: o modelo de dois fatores não ajusta no referencial de origem, CFI = 0,607). Tratamento diferencial (25–27, sem prorating): direção com sinal preservado (−2 a +2, positivo = este filho recebe mais do que os irmãos) e magnitude, a partir de atenção, carinho e permissividade. Perceção estimada pelo progenitor (item 28) e Legitimidade estimada (item 29). Índice de simetria descritiva entre filhos (média das seis amplitudes máx−mín). Coerência espelho (só com exatamente dois filhos). Perfil de fratria (onde o diferencial se concentra). Convergência com o QRF-C, sempre por diferença e nunca por soma, incluindo triangulação relatado · percebido · estimado. Índices de controlo: invariância, variabilidade reduzida, tendência extrema, centralização e indiferenciação entre colunas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qcfp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_qcfp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/QCFP_v1.html</t>
   </si>
   <si>
     <t xml:space="preserve">Resumo por Área Clínica (recalcula automaticamente)</t>
@@ -3986,8 +4025,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M172" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A3:M172"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M174" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A3:M174"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nº"/>
     <tableColumn id="2" name="Nome do Instrumento"/>
@@ -4186,7 +4225,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M172"/>
+  <dimension ref="A1:M174"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -11370,6 +11409,90 @@
       </c>
       <c r="M172" s="7" t="s">
         <v>1159</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A173" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>170</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E173" s="6" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F173" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H173" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I173" s="6" t="s">
+        <v>1162</v>
+      </c>
+      <c r="J173" s="6" t="s">
+        <v>1163</v>
+      </c>
+      <c r="K173" s="6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="L173" s="6" t="s">
+        <v>1165</v>
+      </c>
+      <c r="M173" s="7" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A174" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>171</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E174" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F174" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H174" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I174" s="6" t="s">
+        <v>1168</v>
+      </c>
+      <c r="J174" s="6" t="s">
+        <v>1169</v>
+      </c>
+      <c r="K174" s="6" t="s">
+        <v>1170</v>
+      </c>
+      <c r="L174" s="6" t="s">
+        <v>1171</v>
+      </c>
+      <c r="M174" s="7" t="s">
+        <v>1172</v>
       </c>
     </row>
   </sheetData>
@@ -11553,7 +11676,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1160</v>
+        <v>1173</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11563,10 +11686,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1161</v>
+        <v>1174</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1162</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11579,7 +11702,7 @@
       </c>
       <c r="C3" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B3/$B$29)</f>
-        <v>0.0355029585798817</v>
+        <v>0.0350877192982456</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11592,7 +11715,7 @@
       </c>
       <c r="C4" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B4/$B$29)</f>
-        <v>0.0177514792899408</v>
+        <v>0.0175438596491228</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11605,7 +11728,7 @@
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B5/$B$29)</f>
-        <v>0.130177514792899</v>
+        <v>0.128654970760234</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11618,7 +11741,7 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B6/$B$29)</f>
-        <v>0.0828402366863905</v>
+        <v>0.0818713450292398</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11631,7 +11754,7 @@
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B7/$B$29)</f>
-        <v>0.0355029585798817</v>
+        <v>0.0350877192982456</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11644,7 +11767,7 @@
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B8/$B$29)</f>
-        <v>0.0236686390532544</v>
+        <v>0.0233918128654971</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11657,7 +11780,7 @@
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B9/$B$29)</f>
-        <v>0.0118343195266272</v>
+        <v>0.0116959064327485</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11670,7 +11793,7 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B10/$B$29)</f>
-        <v>0.00591715976331361</v>
+        <v>0.00584795321637427</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11683,7 +11806,7 @@
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B11/$B$29)</f>
-        <v>0.0236686390532544</v>
+        <v>0.0233918128654971</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11696,7 +11819,7 @@
       </c>
       <c r="C12" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B12/$B$29)</f>
-        <v>0.0710059171597633</v>
+        <v>0.0701754385964912</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11709,7 +11832,7 @@
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B13/$B$29)</f>
-        <v>0.0532544378698225</v>
+        <v>0.0526315789473684</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11718,11 +11841,11 @@
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A14)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C14" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B14/$B$29)</f>
-        <v>0.0946745562130178</v>
+        <v>0.105263157894737</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11735,7 +11858,7 @@
       </c>
       <c r="C15" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B15/$B$29)</f>
-        <v>0.00591715976331361</v>
+        <v>0.00584795321637427</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11748,7 +11871,7 @@
       </c>
       <c r="C16" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B16/$B$29)</f>
-        <v>0.0118343195266272</v>
+        <v>0.0116959064327485</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11761,7 +11884,7 @@
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B17/$B$29)</f>
-        <v>0.0177514792899408</v>
+        <v>0.0175438596491228</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11774,7 +11897,7 @@
       </c>
       <c r="C18" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B18/$B$29)</f>
-        <v>0.00591715976331361</v>
+        <v>0.00584795321637427</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11787,7 +11910,7 @@
       </c>
       <c r="C19" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B19/$B$29)</f>
-        <v>0.00591715976331361</v>
+        <v>0.00584795321637427</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11800,7 +11923,7 @@
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B20/$B$29)</f>
-        <v>0.0946745562130178</v>
+        <v>0.0935672514619883</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11813,7 +11936,7 @@
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B21/$B$29)</f>
-        <v>0.0414201183431953</v>
+        <v>0.0409356725146199</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11826,7 +11949,7 @@
       </c>
       <c r="C22" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B22/$B$29)</f>
-        <v>0.00591715976331361</v>
+        <v>0.00584795321637427</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11839,7 +11962,7 @@
       </c>
       <c r="C23" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B23/$B$29)</f>
-        <v>0.0414201183431953</v>
+        <v>0.0409356725146199</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11852,7 +11975,7 @@
       </c>
       <c r="C24" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B24/$B$29)</f>
-        <v>0.0828402366863905</v>
+        <v>0.0818713450292398</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11865,7 +11988,7 @@
       </c>
       <c r="C25" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B25/$B$29)</f>
-        <v>0.0355029585798817</v>
+        <v>0.0350877192982456</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11878,7 +12001,7 @@
       </c>
       <c r="C26" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B26/$B$29)</f>
-        <v>0.0177514792899408</v>
+        <v>0.0175438596491228</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11891,7 +12014,7 @@
       </c>
       <c r="C27" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B27/$B$29)</f>
-        <v>0.0177514792899408</v>
+        <v>0.0175438596491228</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11904,16 +12027,16 @@
       </c>
       <c r="C28" s="10" t="n">
         <f aca="false">IF($B$29=0,0,B28/$B$29)</f>
-        <v>0.029585798816568</v>
+        <v>0.0292397660818713</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>1163</v>
+        <v>1176</v>
       </c>
       <c r="B29" s="11" t="n">
         <f aca="false">COUNTA(Catálogo!$B$4:$B$1000)</f>
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">IF(B29=0,0,B29/B29)</f>
@@ -11923,12 +12046,12 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>1164</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>1165</v>
+        <v>1178</v>
       </c>
       <c r="B32" s="15" t="str">
         <f aca="false">IF(SUM(B3:B28)=B29,"OK","Existe AREA nova - adicionar linha no resumo")</f>
@@ -11964,64 +12087,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1166</v>
+        <v>1179</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1168</v>
+        <v>1181</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>1170</v>
+        <v>1183</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1171</v>
+        <v>1184</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1172</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1174</v>
+        <v>1187</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1175</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>1176</v>
+        <v>1189</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1178</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>1179</v>
+        <v>1192</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1180</v>
+        <v>1193</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1181</v>
+        <v>1194</v>
       </c>
     </row>
   </sheetData>
@@ -12052,56 +12175,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1182</v>
+        <v>1195</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>1183</v>
+        <v>1196</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>1184</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>1186</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>1187</v>
+        <v>1200</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>1188</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>1189</v>
+        <v>1202</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1190</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>1191</v>
+        <v>1204</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>1192</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>1193</v>
+        <v>1206</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>1194</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12110,18 +12233,18 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>1195</v>
+        <v>1208</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>1197</v>
+        <v>1210</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
     </row>
   </sheetData>
